--- a/demo_data/labs.xlsx
+++ b/demo_data/labs.xlsx
@@ -481,46 +481,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1019</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Haemoglobin</t>
+          <t>Creatinine</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11.38</v>
+        <v>1.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>g/dL</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>0.7</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LIS-174161</t>
+          <t>LIS-688936</t>
         </is>
       </c>
     </row>
@@ -532,46 +532,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UHID-1013</t>
+          <t>UHID-1003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Platelets</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>527.88</v>
+        <v>14.29</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>x10^9/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>400</v>
+        <v>16</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LIS-959588</t>
+          <t>LIS-936488</t>
         </is>
       </c>
     </row>
@@ -583,46 +583,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1017</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Haemoglobin</t>
+          <t>Glucose_fasting</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18.54</v>
+        <v>3.21</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>g/dL</t>
+          <t>mmol/L</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LIS-796247</t>
+          <t>LIS-458404</t>
         </is>
       </c>
     </row>
@@ -634,46 +634,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1019</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HbA1c</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6.64</v>
+        <v>39.63</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>U/L</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LIS-320751</t>
+          <t>LIS-840940</t>
         </is>
       </c>
     </row>
@@ -685,46 +685,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HbA1c</t>
+          <t>Platelets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.64</v>
+        <v>376.3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x10^9/L</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6</v>
+        <v>400</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LIS-715561</t>
+          <t>LIS-763433</t>
         </is>
       </c>
     </row>
@@ -736,32 +736,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UHID-1000</t>
+          <t>UHID-1004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALT</t>
+          <t>Creatinine</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50.57</v>
+        <v>1.67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>40</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -770,12 +770,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LIS-447789</t>
+          <t>LIS-960476</t>
         </is>
       </c>
     </row>
@@ -787,46 +787,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1014</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Urea</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.32</v>
+        <v>52.79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>U/L</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1</v>
+        <v>40</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LIS-755923</t>
+          <t>LIS-537253</t>
         </is>
       </c>
     </row>
@@ -838,46 +838,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UHID-1001</t>
+          <t>UHID-1005</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Potassium</t>
+          <t>Platelets</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.98</v>
+        <v>434.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>x10^9/L</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LIS-859429</t>
+          <t>LIS-607281</t>
         </is>
       </c>
     </row>
@@ -889,46 +889,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1011</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glucose_fasting</t>
+          <t>Creatinine</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.32</v>
+        <v>1.17</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LIS-429774</t>
+          <t>LIS-539027</t>
         </is>
       </c>
     </row>
@@ -940,36 +940,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HbA1c</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.46</v>
+        <v>18.74</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LIS-171971</t>
+          <t>LIS-928013</t>
         </is>
       </c>
     </row>
@@ -991,46 +991,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UHID-1019</t>
+          <t>UHID-1017</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>155.56</v>
+        <v>14.03</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LIS-155573</t>
+          <t>LIS-455716</t>
         </is>
       </c>
     </row>
@@ -1042,21 +1042,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UHID-1008</t>
+          <t>UHID-1014</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Urea</t>
+          <t>Sodium</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.130000000000001</v>
+        <v>179.95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>136</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1</v>
+        <v>145</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LIS-296559</t>
+          <t>LIS-336763</t>
         </is>
       </c>
     </row>
@@ -1093,46 +1093,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UHID-1009</t>
+          <t>UHID-1013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>Creatinine</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.48</v>
+        <v>0.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>mIU/L</t>
+          <t>mg/dL</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LIS-709289</t>
+          <t>LIS-275955</t>
         </is>
       </c>
     </row>
@@ -1144,32 +1144,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HbA1c</t>
+          <t>Platelets</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.24</v>
+        <v>193.84</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x10^9/L</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
+        <v>400</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LIS-409991</t>
+          <t>LIS-774029</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UHID-1010</t>
+          <t>UHID-1019</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103.34</v>
+        <v>9.82</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LIS-558264</t>
+          <t>LIS-947838</t>
         </is>
       </c>
     </row>
@@ -1246,21 +1246,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UHID-1004</t>
+          <t>UHID-1014</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Urea</t>
+          <t>Sodium</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.609999999999999</v>
+        <v>197.09</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
-        <v>7.1</v>
+        <v>145</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LIS-516503</t>
+          <t>LIS-575313</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UHID-1000</t>
+          <t>UHID-1013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>547.83</v>
+        <v>120.71</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LIS-592482</t>
+          <t>LIS-100553</t>
         </is>
       </c>
     </row>
@@ -1348,46 +1348,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UHID-1018</t>
+          <t>UHID-1000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Urea</t>
+          <t>HbA1c</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.9</v>
+        <v>6.16</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LIS-267284</t>
+          <t>LIS-280852</t>
         </is>
       </c>
     </row>
@@ -1399,21 +1399,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UHID-1008</t>
+          <t>UHID-1000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>Potassium</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>170.56</v>
+        <v>4.81</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1421,14 +1421,14 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>136</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LIS-135722</t>
+          <t>LIS-840263</t>
         </is>
       </c>
     </row>
@@ -1450,46 +1450,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UHID-1011</t>
+          <t>UHID-1004</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ALT</t>
+          <t>HbA1c</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>44.08</v>
+        <v>4.97</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LIS-623432</t>
+          <t>LIS-812373</t>
         </is>
       </c>
     </row>
@@ -1501,32 +1501,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1010</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>Glucose_fasting</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.42</v>
+        <v>4.84</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>mIU/L</t>
+          <t>mmol/L</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LIS-173616</t>
+          <t>LIS-364221</t>
         </is>
       </c>
     </row>
@@ -1552,21 +1552,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UHID-1008</t>
+          <t>UHID-1018</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>Potassium</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>134.27</v>
+        <v>5.62</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1574,24 +1574,24 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>136</v>
+        <v>3.5</v>
       </c>
       <c r="H23" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LIS-625775</t>
+          <t>LIS-927311</t>
         </is>
       </c>
     </row>
@@ -1608,31 +1608,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Urea</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.6</v>
+        <v>19.63</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>7.1</v>
+        <v>16</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LIS-411330</t>
+          <t>LIS-204148</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UHID-1003</t>
+          <t>UHID-1005</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.87</v>
+        <v>2.43</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1683,17 +1683,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LIS-770876</t>
+          <t>LIS-165107</t>
         </is>
       </c>
     </row>
@@ -1705,46 +1705,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UHID-1015</t>
+          <t>UHID-1012</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALT</t>
+          <t>Platelets</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24.47</v>
+        <v>108.05</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>U/L</t>
+          <t>x10^9/L</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="H26" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LIS-543036</t>
+          <t>LIS-115272</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UHID-1006</t>
+          <t>UHID-1008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Platelets</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>226.87</v>
+        <v>0.98</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>x10^9/L</t>
+          <t>mIU/L</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LIS-695048</t>
+          <t>LIS-961293</t>
         </is>
       </c>
     </row>
@@ -1807,46 +1807,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UHID-1013</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Creatinine</t>
+          <t>HbA1c</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.82</v>
+        <v>6.22</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>mg/dL</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LIS-585415</t>
+          <t>LIS-151073</t>
         </is>
       </c>
     </row>
@@ -1858,46 +1858,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UHID-1017</t>
+          <t>UHID-1015</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>125.41</v>
+        <v>12.93</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="H29" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LIS-203202</t>
+          <t>LIS-487971</t>
         </is>
       </c>
     </row>
@@ -1909,46 +1909,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UHID-1005</t>
+          <t>UHID-1006</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sodium</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101.02</v>
+        <v>0.48</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>mIU/L</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>136</v>
+        <v>0.4</v>
       </c>
       <c r="H30" t="n">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LIS-734576</t>
+          <t>LIS-676000</t>
         </is>
       </c>
     </row>
@@ -1960,46 +1960,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UHID-1010</t>
+          <t>UHID-1015</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Glucose_fasting</t>
+          <t>Haemoglobin</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.85</v>
+        <v>19.15</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>mmol/L</t>
+          <t>g/dL</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LIS-254689</t>
+          <t>LIS-775656</t>
         </is>
       </c>
     </row>
